--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/17.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/17.xlsx
@@ -426,13 +426,13 @@
         <v>-21.02485596807889</v>
       </c>
       <c r="E2">
-        <v>-25.09646539166615</v>
+        <v>-29.28746393086289</v>
       </c>
       <c r="F2">
-        <v>-4.391800066576151</v>
+        <v>-5.166163368018719</v>
       </c>
       <c r="G2">
-        <v>-18.02145899661301</v>
+        <v>-18.39989407829818</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.76775491346561</v>
       </c>
       <c r="E3">
-        <v>-24.49970308693535</v>
+        <v>-29.37923345662833</v>
       </c>
       <c r="F3">
-        <v>-4.05308813132337</v>
+        <v>-4.177624429689866</v>
       </c>
       <c r="G3">
-        <v>-17.51294264905326</v>
+        <v>-20.07399060987007</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.4163429010802</v>
       </c>
       <c r="E4">
-        <v>-23.62034589022989</v>
+        <v>-32.00526157012131</v>
       </c>
       <c r="F4">
-        <v>-3.431741703577603</v>
+        <v>-5.719179220336935</v>
       </c>
       <c r="G4">
-        <v>-17.02193743212348</v>
+        <v>-18.43133929510294</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.98285131341382</v>
       </c>
       <c r="E5">
-        <v>-25.96715961759493</v>
+        <v>-32.55282200475877</v>
       </c>
       <c r="F5">
-        <v>-3.793319976690456</v>
+        <v>-4.497017528333159</v>
       </c>
       <c r="G5">
-        <v>-17.1987023559201</v>
+        <v>-17.3462649575148</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.45852571856818</v>
       </c>
       <c r="E6">
-        <v>-25.94848871926131</v>
+        <v>-30.58506192996877</v>
       </c>
       <c r="F6">
-        <v>-3.555324610983005</v>
+        <v>-5.120038725084503</v>
       </c>
       <c r="G6">
-        <v>-18.00148316482905</v>
+        <v>-17.56229295140718</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.84276951182716</v>
       </c>
       <c r="E7">
-        <v>-27.22880153307991</v>
+        <v>-32.97142961355381</v>
       </c>
       <c r="F7">
-        <v>-3.294416979943933</v>
+        <v>-4.571815166866406</v>
       </c>
       <c r="G7">
-        <v>-16.55629264929729</v>
+        <v>-17.80810757878914</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.14625249251232</v>
       </c>
       <c r="E8">
-        <v>-29.18418755264396</v>
+        <v>-32.49380466725381</v>
       </c>
       <c r="F8">
-        <v>-3.593253575804822</v>
+        <v>-4.730717883597938</v>
       </c>
       <c r="G8">
-        <v>-17.12087805138291</v>
+        <v>-19.38789328903827</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.3984571332467</v>
       </c>
       <c r="E9">
-        <v>-30.12222471554081</v>
+        <v>-31.35213561365404</v>
       </c>
       <c r="F9">
-        <v>-3.428681983748974</v>
+        <v>-4.089774678854524</v>
       </c>
       <c r="G9">
-        <v>-15.36625415484102</v>
+        <v>-18.67502193115762</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.63089505535791</v>
       </c>
       <c r="E10">
-        <v>-29.03737442531529</v>
+        <v>-36.40706736708611</v>
       </c>
       <c r="F10">
-        <v>-3.124356263185172</v>
+        <v>-4.550031291999536</v>
       </c>
       <c r="G10">
-        <v>-16.40753825130845</v>
+        <v>-15.827265829185</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.86622583912699</v>
       </c>
       <c r="E11">
-        <v>-29.66197099553423</v>
+        <v>-34.17533122120399</v>
       </c>
       <c r="F11">
-        <v>-3.286665531340815</v>
+        <v>-4.599758074038419</v>
       </c>
       <c r="G11">
-        <v>-15.78946105439929</v>
+        <v>-17.7470379452262</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.1308195057303</v>
       </c>
       <c r="E12">
-        <v>-30.76763641653601</v>
+        <v>-36.76464020320577</v>
       </c>
       <c r="F12">
-        <v>-3.001421883352143</v>
+        <v>-5.277132849660603</v>
       </c>
       <c r="G12">
-        <v>-14.39830526315952</v>
+        <v>-18.28435769425038</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.44506331366422</v>
       </c>
       <c r="E13">
-        <v>-31.90956812162822</v>
+        <v>-35.79794006407737</v>
       </c>
       <c r="F13">
-        <v>-3.228689225188407</v>
+        <v>-4.830516695565271</v>
       </c>
       <c r="G13">
-        <v>-14.12143275280089</v>
+        <v>-16.54718533851876</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.84643365565643</v>
       </c>
       <c r="E14">
-        <v>-31.4252591476929</v>
+        <v>-37.4603632504262</v>
       </c>
       <c r="F14">
-        <v>-3.46577791925927</v>
+        <v>-5.661864903257181</v>
       </c>
       <c r="G14">
-        <v>-14.45294085146688</v>
+        <v>-16.53504722329902</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.34956304198671</v>
       </c>
       <c r="E15">
-        <v>-33.88514434255546</v>
+        <v>-35.42539382865135</v>
       </c>
       <c r="F15">
-        <v>-3.297648531864387</v>
+        <v>-4.570661437107009</v>
       </c>
       <c r="G15">
-        <v>-14.60802832307235</v>
+        <v>-13.43311902173055</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.95289129174298</v>
       </c>
       <c r="E16">
-        <v>-35.20513338139227</v>
+        <v>-38.58420823033177</v>
       </c>
       <c r="F16">
-        <v>-2.884075609841741</v>
+        <v>-3.286359084246177</v>
       </c>
       <c r="G16">
-        <v>-12.73668617772515</v>
+        <v>-14.76649255112788</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.65702584886256</v>
       </c>
       <c r="E17">
-        <v>-35.4315616102498</v>
+        <v>-39.36947505834286</v>
       </c>
       <c r="F17">
-        <v>-2.507236746527713</v>
+        <v>-3.52791699641041</v>
       </c>
       <c r="G17">
-        <v>-14.24811408840664</v>
+        <v>-15.80514145334605</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.45801278235613</v>
       </c>
       <c r="E18">
-        <v>-35.40377036526473</v>
+        <v>-39.73795472410999</v>
       </c>
       <c r="F18">
-        <v>-2.308355749519785</v>
+        <v>-5.063174180484734</v>
       </c>
       <c r="G18">
-        <v>-13.47501728607556</v>
+        <v>-16.44132402380949</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.3505130327068</v>
       </c>
       <c r="E19">
-        <v>-35.96760839972276</v>
+        <v>-37.59607482372506</v>
       </c>
       <c r="F19">
-        <v>-2.78955133042578</v>
+        <v>-3.634822688673276</v>
       </c>
       <c r="G19">
-        <v>-12.94520088851614</v>
+        <v>-13.95709396168593</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.31276941465605</v>
       </c>
       <c r="E20">
-        <v>-36.43831836621305</v>
+        <v>-36.82887207853057</v>
       </c>
       <c r="F20">
-        <v>-2.474419984400935</v>
+        <v>-2.960360348229586</v>
       </c>
       <c r="G20">
-        <v>-11.97426422948545</v>
+        <v>-13.84193332455684</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.32115428928962</v>
       </c>
       <c r="E21">
-        <v>-37.04456782398992</v>
+        <v>-43.04814242644481</v>
       </c>
       <c r="F21">
-        <v>-2.123985457962071</v>
+        <v>-4.005174692557665</v>
       </c>
       <c r="G21">
-        <v>-11.39654423797278</v>
+        <v>-13.66262590178606</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.35412378339934</v>
       </c>
       <c r="E22">
-        <v>-37.45569892219829</v>
+        <v>-39.48034568747266</v>
       </c>
       <c r="F22">
-        <v>-2.119091014830405</v>
+        <v>-3.406849013998726</v>
       </c>
       <c r="G22">
-        <v>-10.88895153261848</v>
+        <v>-15.49211944097134</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.40316664051294</v>
       </c>
       <c r="E23">
-        <v>-38.42272284721825</v>
+        <v>-42.77815933458151</v>
       </c>
       <c r="F23">
-        <v>-1.962582861443018</v>
+        <v>-2.861913229261082</v>
       </c>
       <c r="G23">
-        <v>-10.7966700757113</v>
+        <v>-11.51497238354913</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.45425192889816</v>
       </c>
       <c r="E24">
-        <v>-38.21029213151843</v>
+        <v>-42.38577159029088</v>
       </c>
       <c r="F24">
-        <v>-2.192923384608192</v>
+        <v>-3.452169134327899</v>
       </c>
       <c r="G24">
-        <v>-12.0695185562869</v>
+        <v>-12.83113935250609</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.48710970964003</v>
       </c>
       <c r="E25">
-        <v>-38.2433952765145</v>
+        <v>-40.87270426942604</v>
       </c>
       <c r="F25">
-        <v>-1.548634601118412</v>
+        <v>-3.18235315751448</v>
       </c>
       <c r="G25">
-        <v>-11.70728528447093</v>
+        <v>-15.02622802250248</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.4936166667417</v>
       </c>
       <c r="E26">
-        <v>-38.29833019470155</v>
+        <v>-41.69846244777671</v>
       </c>
       <c r="F26">
-        <v>-1.722975283113649</v>
+        <v>-3.290068915353094</v>
       </c>
       <c r="G26">
-        <v>-12.08031424529047</v>
+        <v>-15.51615731213199</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.46862273671615</v>
       </c>
       <c r="E27">
-        <v>-38.7740350680223</v>
+        <v>-41.04542253231559</v>
       </c>
       <c r="F27">
-        <v>-2.136193455011236</v>
+        <v>-3.873480043453382</v>
       </c>
       <c r="G27">
-        <v>-12.62908351606221</v>
+        <v>-13.43674737964159</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.41734398608882</v>
       </c>
       <c r="E28">
-        <v>-38.91654161656968</v>
+        <v>-41.91289022051392</v>
       </c>
       <c r="F28">
-        <v>-2.405658640964385</v>
+        <v>-4.07172201512443</v>
       </c>
       <c r="G28">
-        <v>-11.29186478802102</v>
+        <v>-14.51417435703402</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.33816143417206</v>
       </c>
       <c r="E29">
-        <v>-36.98917100145409</v>
+        <v>-40.88896601958758</v>
       </c>
       <c r="F29">
-        <v>-2.060347403161968</v>
+        <v>-3.426739568443687</v>
       </c>
       <c r="G29">
-        <v>-12.55534442472049</v>
+        <v>-13.91632624864257</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.22822278164061</v>
       </c>
       <c r="E30">
-        <v>-38.63787291155967</v>
+        <v>-40.38943684451248</v>
       </c>
       <c r="F30">
-        <v>-1.578685420863876</v>
+        <v>-3.131443347156763</v>
       </c>
       <c r="G30">
-        <v>-11.80851183542522</v>
+        <v>-12.60536345727334</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.09213484459161</v>
       </c>
       <c r="E31">
-        <v>-38.32539009113438</v>
+        <v>-42.15949732954962</v>
       </c>
       <c r="F31">
-        <v>-1.989056881378461</v>
+        <v>-3.772287570280463</v>
       </c>
       <c r="G31">
-        <v>-11.10988078918175</v>
+        <v>-13.94057102889942</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.94100163654986</v>
       </c>
       <c r="E32">
-        <v>-38.76184894446766</v>
+        <v>-41.29298967784092</v>
       </c>
       <c r="F32">
-        <v>-2.285769727606746</v>
+        <v>-3.287314850766145</v>
       </c>
       <c r="G32">
-        <v>-11.82421375291799</v>
+        <v>-14.58361139444746</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.78429766566619</v>
       </c>
       <c r="E33">
-        <v>-37.554709477902</v>
+        <v>-40.15886053346393</v>
       </c>
       <c r="F33">
-        <v>-1.93611359262532</v>
+        <v>-3.773164151504659</v>
       </c>
       <c r="G33">
-        <v>-11.85449862351124</v>
+        <v>-16.28069138842574</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.62281573503378</v>
       </c>
       <c r="E34">
-        <v>-38.40419233157886</v>
+        <v>-40.63354650013295</v>
       </c>
       <c r="F34">
-        <v>-1.620237112967261</v>
+        <v>-2.930288148454264</v>
       </c>
       <c r="G34">
-        <v>-11.36174378326396</v>
+        <v>-13.68673991549411</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.46114933353989</v>
       </c>
       <c r="E35">
-        <v>-37.86001919549913</v>
+        <v>-39.44592249230335</v>
       </c>
       <c r="F35">
-        <v>-1.864678161750551</v>
+        <v>-3.399534668228269</v>
       </c>
       <c r="G35">
-        <v>-11.41550704282172</v>
+        <v>-13.75499674342281</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.30173471229424</v>
       </c>
       <c r="E36">
-        <v>-36.58537150266413</v>
+        <v>-41.01186880415576</v>
       </c>
       <c r="F36">
-        <v>-1.561257529117423</v>
+        <v>-4.02458142484546</v>
       </c>
       <c r="G36">
-        <v>-12.1467701364458</v>
+        <v>-12.99488224542399</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.15766720717233</v>
       </c>
       <c r="E37">
-        <v>-37.33122928562346</v>
+        <v>-39.79912987947962</v>
       </c>
       <c r="F37">
-        <v>-1.166236138188234</v>
+        <v>-2.554584010428649</v>
       </c>
       <c r="G37">
-        <v>-11.04671226974691</v>
+        <v>-12.99205503953345</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.03164025609109</v>
       </c>
       <c r="E38">
-        <v>-37.44178292157272</v>
+        <v>-39.76598824245448</v>
       </c>
       <c r="F38">
-        <v>-1.847391219830572</v>
+        <v>-3.018677943006771</v>
       </c>
       <c r="G38">
-        <v>-12.50589149545486</v>
+        <v>-16.05773111217413</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.91900455749729</v>
       </c>
       <c r="E39">
-        <v>-36.08556382643755</v>
+        <v>-40.42273924236488</v>
       </c>
       <c r="F39">
-        <v>-1.825168658425125</v>
+        <v>-2.822567639497904</v>
       </c>
       <c r="G39">
-        <v>-11.78244791039454</v>
+        <v>-14.81606797057846</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.82352468724753</v>
       </c>
       <c r="E40">
-        <v>-35.36382016756906</v>
+        <v>-39.43269934820095</v>
       </c>
       <c r="F40">
-        <v>-1.661752379834591</v>
+        <v>-2.481621887051396</v>
       </c>
       <c r="G40">
-        <v>-11.97336045055323</v>
+        <v>-13.63432239269806</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.75044055631299</v>
       </c>
       <c r="E41">
-        <v>-37.6831777570256</v>
+        <v>-38.61305008128662</v>
       </c>
       <c r="F41">
-        <v>-1.822580882959297</v>
+        <v>-3.164234769988895</v>
       </c>
       <c r="G41">
-        <v>-11.55760558900386</v>
+        <v>-13.48643701291328</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.70686921045909</v>
       </c>
       <c r="E42">
-        <v>-34.89314416463382</v>
+        <v>-38.43424781356777</v>
       </c>
       <c r="F42">
-        <v>-1.85718089794686</v>
+        <v>-3.255030213826954</v>
       </c>
       <c r="G42">
-        <v>-12.49621146029803</v>
+        <v>-14.87070190361305</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.69048687137489</v>
       </c>
       <c r="E43">
-        <v>-35.33959283162802</v>
+        <v>-37.52520646974202</v>
       </c>
       <c r="F43">
-        <v>-1.942972622945089</v>
+        <v>-2.259709846768189</v>
       </c>
       <c r="G43">
-        <v>-10.28821331797126</v>
+        <v>-14.01744686213961</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.69939562491795</v>
       </c>
       <c r="E44">
-        <v>-34.63628006197074</v>
+        <v>-39.48909922772948</v>
       </c>
       <c r="F44">
-        <v>-1.569262370667011</v>
+        <v>-2.506561295954779</v>
       </c>
       <c r="G44">
-        <v>-12.40117231895663</v>
+        <v>-14.59446998381627</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.73290233329162</v>
       </c>
       <c r="E45">
-        <v>-34.51531320004085</v>
+        <v>-37.97231629394135</v>
       </c>
       <c r="F45">
-        <v>-1.477740005813766</v>
+        <v>-2.616444355338671</v>
       </c>
       <c r="G45">
-        <v>-12.60376777432341</v>
+        <v>-14.16986272349488</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.79802091234237</v>
       </c>
       <c r="E46">
-        <v>-33.68381970935946</v>
+        <v>-34.67113119793378</v>
       </c>
       <c r="F46">
-        <v>-1.209279681263963</v>
+        <v>-3.001063965815253</v>
       </c>
       <c r="G46">
-        <v>-12.36098891720096</v>
+        <v>-14.54354551705843</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.89394672080073</v>
       </c>
       <c r="E47">
-        <v>-32.56011511214813</v>
+        <v>-38.02868673838883</v>
       </c>
       <c r="F47">
-        <v>-1.939268334808876</v>
+        <v>-2.71283424032302</v>
       </c>
       <c r="G47">
-        <v>-11.90142229598487</v>
+        <v>-15.48788856377215</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.00884881217586</v>
       </c>
       <c r="E48">
-        <v>-32.30119281804856</v>
+        <v>-34.18620861577041</v>
       </c>
       <c r="F48">
-        <v>-1.758787624979481</v>
+        <v>-3.170862579245009</v>
       </c>
       <c r="G48">
-        <v>-11.53173036506892</v>
+        <v>-15.47013741859058</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.13977240275278</v>
       </c>
       <c r="E49">
-        <v>-33.06195833744115</v>
+        <v>-37.52662841058044</v>
       </c>
       <c r="F49">
-        <v>-1.134601612527331</v>
+        <v>-2.698973646151094</v>
       </c>
       <c r="G49">
-        <v>-12.02135342923605</v>
+        <v>-15.94517421911168</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.28248931957478</v>
       </c>
       <c r="E50">
-        <v>-32.25688849259452</v>
+        <v>-35.91124248374928</v>
       </c>
       <c r="F50">
-        <v>-1.587769557994837</v>
+        <v>-1.974477284720926</v>
       </c>
       <c r="G50">
-        <v>-13.83372317161944</v>
+        <v>-14.62865302178201</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.43796148154817</v>
       </c>
       <c r="E51">
-        <v>-31.97887188784161</v>
+        <v>-35.32349184229375</v>
       </c>
       <c r="F51">
-        <v>-1.446049258592865</v>
+        <v>-2.769866657749826</v>
       </c>
       <c r="G51">
-        <v>-13.58418583577857</v>
+        <v>-16.08436114049203</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.59881235712852</v>
       </c>
       <c r="E52">
-        <v>-32.72427908763719</v>
+        <v>-35.70822420127441</v>
       </c>
       <c r="F52">
-        <v>-2.320056168823052</v>
+        <v>-3.383916952343163</v>
       </c>
       <c r="G52">
-        <v>-13.0238660716203</v>
+        <v>-16.47055448564848</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.75492991175435</v>
       </c>
       <c r="E53">
-        <v>-31.11131815863714</v>
+        <v>-33.78581905790823</v>
       </c>
       <c r="F53">
-        <v>-1.875869419602004</v>
+        <v>-2.956817598096748</v>
       </c>
       <c r="G53">
-        <v>-13.96591325500254</v>
+        <v>-15.22877050914063</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.90358749826969</v>
       </c>
       <c r="E54">
-        <v>-30.42581134877803</v>
+        <v>-33.90926299512032</v>
       </c>
       <c r="F54">
-        <v>-1.179032481984985</v>
+        <v>-2.933457935844016</v>
       </c>
       <c r="G54">
-        <v>-13.08956715839268</v>
+        <v>-16.59558882484844</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.0470538766759</v>
       </c>
       <c r="E55">
-        <v>-30.33904125831706</v>
+        <v>-32.27832628854683</v>
       </c>
       <c r="F55">
-        <v>-1.782074436760102</v>
+        <v>-2.770091543989818</v>
       </c>
       <c r="G55">
-        <v>-13.29076887408743</v>
+        <v>-15.91731763367148</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.18542302416093</v>
       </c>
       <c r="E56">
-        <v>-30.57255202052258</v>
+        <v>-33.05781704796114</v>
       </c>
       <c r="F56">
-        <v>-1.873803475235313</v>
+        <v>-3.207595054247712</v>
       </c>
       <c r="G56">
-        <v>-14.13869724778819</v>
+        <v>-14.85266439624234</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.31023795717259</v>
       </c>
       <c r="E57">
-        <v>-29.48782626333226</v>
+        <v>-33.3365174522892</v>
       </c>
       <c r="F57">
-        <v>-1.801264201337482</v>
+        <v>-3.000992699049058</v>
       </c>
       <c r="G57">
-        <v>-13.36842103025657</v>
+        <v>-16.02961630418187</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.42005004538759</v>
       </c>
       <c r="E58">
-        <v>-30.67559291809311</v>
+        <v>-34.77998212765615</v>
       </c>
       <c r="F58">
-        <v>-1.883689759412444</v>
+        <v>-3.552309234920008</v>
       </c>
       <c r="G58">
-        <v>-13.63149518680753</v>
+        <v>-16.30891875496634</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.51338421997161</v>
       </c>
       <c r="E59">
-        <v>-28.6830937897992</v>
+        <v>-35.85756195286236</v>
       </c>
       <c r="F59">
-        <v>-1.687512148402171</v>
+        <v>-4.143232672030183</v>
       </c>
       <c r="G59">
-        <v>-12.90560345332092</v>
+        <v>-14.17907597173068</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.59776674954046</v>
       </c>
       <c r="E60">
-        <v>-30.10912836871063</v>
+        <v>-31.2922488091396</v>
       </c>
       <c r="F60">
-        <v>-2.095477167778246</v>
+        <v>-4.109908332157506</v>
       </c>
       <c r="G60">
-        <v>-14.07327921265942</v>
+        <v>-15.29223201185569</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.67178251758469</v>
       </c>
       <c r="E61">
-        <v>-28.92911672568792</v>
+        <v>-32.0501817680404</v>
       </c>
       <c r="F61">
-        <v>-1.655131697255096</v>
+        <v>-3.738262440540204</v>
       </c>
       <c r="G61">
-        <v>-13.46888615573683</v>
+        <v>-17.62119417764189</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.72728858508885</v>
       </c>
       <c r="E62">
-        <v>-29.23207163680106</v>
+        <v>-30.50903337985399</v>
       </c>
       <c r="F62">
-        <v>-2.085601177689565</v>
+        <v>-3.916070646637295</v>
       </c>
       <c r="G62">
-        <v>-13.72697794125119</v>
+        <v>-13.35864829982464</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.76574216105627</v>
       </c>
       <c r="E63">
-        <v>-28.07160488759546</v>
+        <v>-33.41204560602613</v>
       </c>
       <c r="F63">
-        <v>-2.285872668491249</v>
+        <v>-3.950961271660341</v>
       </c>
       <c r="G63">
-        <v>-13.59401153493913</v>
+        <v>-15.98617863616109</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.79003887413054</v>
       </c>
       <c r="E64">
-        <v>-28.15775457711738</v>
+        <v>-32.15414421007149</v>
       </c>
       <c r="F64">
-        <v>-2.316887173286258</v>
+        <v>-3.72810296709266</v>
       </c>
       <c r="G64">
-        <v>-13.56902684775425</v>
+        <v>-15.40463330927779</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.80442505492611</v>
       </c>
       <c r="E65">
-        <v>-25.39406311802822</v>
+        <v>-30.17826005291172</v>
       </c>
       <c r="F65">
-        <v>-2.271300198510333</v>
+        <v>-3.983376564337556</v>
       </c>
       <c r="G65">
-        <v>-13.81776137630185</v>
+        <v>-14.54953098339343</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.80401023373976</v>
       </c>
       <c r="E66">
-        <v>-28.4082108890596</v>
+        <v>-31.84474980891943</v>
       </c>
       <c r="F66">
-        <v>-2.111768750530371</v>
+        <v>-3.537743891615711</v>
       </c>
       <c r="G66">
-        <v>-13.84648366940057</v>
+        <v>-15.18847620410939</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.78604696237677</v>
       </c>
       <c r="E67">
-        <v>-27.87906775821134</v>
+        <v>-30.34283838377249</v>
       </c>
       <c r="F67">
-        <v>-1.909046474824545</v>
+        <v>-3.737394569698543</v>
       </c>
       <c r="G67">
-        <v>-14.3524608285317</v>
+        <v>-17.41723808805847</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.74870082679957</v>
       </c>
       <c r="E68">
-        <v>-27.98988857412705</v>
+        <v>-30.35899371479485</v>
       </c>
       <c r="F68">
-        <v>-2.300829979009617</v>
+        <v>-3.558976636824008</v>
       </c>
       <c r="G68">
-        <v>-13.5505275192808</v>
+        <v>-15.60834276321853</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.7004538836347</v>
       </c>
       <c r="E69">
-        <v>-26.10662756008317</v>
+        <v>-29.56937275902538</v>
       </c>
       <c r="F69">
-        <v>-1.950008236474428</v>
+        <v>-4.097697959549468</v>
       </c>
       <c r="G69">
-        <v>-13.54030786520107</v>
+        <v>-15.96321007120963</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.64213082894979</v>
       </c>
       <c r="E70">
-        <v>-27.6100673452077</v>
+        <v>-32.32821875092634</v>
       </c>
       <c r="F70">
-        <v>-2.267266499543709</v>
+        <v>-3.372912571789731</v>
       </c>
       <c r="G70">
-        <v>-13.71038052119005</v>
+        <v>-16.51838855814541</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.56565737857596</v>
       </c>
       <c r="E71">
-        <v>-25.58817615636701</v>
+        <v>-32.46608134937885</v>
       </c>
       <c r="F71">
-        <v>-2.675514210425689</v>
+        <v>-4.323995281512526</v>
       </c>
       <c r="G71">
-        <v>-13.98775457919789</v>
+        <v>-14.19489210304454</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.47279939772706</v>
       </c>
       <c r="E72">
-        <v>-26.35373280125971</v>
+        <v>-30.68600840831075</v>
       </c>
       <c r="F72">
-        <v>-2.004262041872595</v>
+        <v>-4.324067340131679</v>
       </c>
       <c r="G72">
-        <v>-13.76230477270075</v>
+        <v>-15.40731816171014</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.36498144876462</v>
       </c>
       <c r="E73">
-        <v>-27.2334568043598</v>
+        <v>-31.74903824653032</v>
       </c>
       <c r="F73">
-        <v>-2.562573806772041</v>
+        <v>-3.297068895499336</v>
       </c>
       <c r="G73">
-        <v>-13.06605235342724</v>
+        <v>-16.65306155068296</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.24900615685533</v>
       </c>
       <c r="E74">
-        <v>-26.26770990901001</v>
+        <v>-31.33713277926663</v>
       </c>
       <c r="F74">
-        <v>-2.038669636591433</v>
+        <v>-4.014671385079597</v>
       </c>
       <c r="G74">
-        <v>-13.49314748872138</v>
+        <v>-14.93861609007844</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.12283770323387</v>
       </c>
       <c r="E75">
-        <v>-25.65969887484416</v>
+        <v>-30.39909335213277</v>
       </c>
       <c r="F75">
-        <v>-2.704885620333429</v>
+        <v>-4.119889638689563</v>
       </c>
       <c r="G75">
-        <v>-13.94212698530288</v>
+        <v>-16.34145314125352</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.98296729235878</v>
       </c>
       <c r="E76">
-        <v>-27.84063007083423</v>
+        <v>-32.21659413087426</v>
       </c>
       <c r="F76">
-        <v>-2.811347874939973</v>
+        <v>-3.289782264582399</v>
       </c>
       <c r="G76">
-        <v>-13.86348166547195</v>
+        <v>-14.44775322660685</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.82951687215023</v>
       </c>
       <c r="E77">
-        <v>-28.24523110952355</v>
+        <v>-32.67878603775613</v>
       </c>
       <c r="F77">
-        <v>-2.619561088580256</v>
+        <v>-4.12695771819017</v>
       </c>
       <c r="G77">
-        <v>-14.32645152750241</v>
+        <v>-16.03536341123805</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.67054069439496</v>
       </c>
       <c r="E78">
-        <v>-27.74942660431975</v>
+        <v>-31.69268818021587</v>
       </c>
       <c r="F78">
-        <v>-2.593118742763121</v>
+        <v>-5.063721350878517</v>
       </c>
       <c r="G78">
-        <v>-13.9748451068675</v>
+        <v>-17.52505593518145</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.50991735544909</v>
       </c>
       <c r="E79">
-        <v>-26.67020973575977</v>
+        <v>-31.17771690877461</v>
       </c>
       <c r="F79">
-        <v>-2.883328100649654</v>
+        <v>-5.468104027473869</v>
       </c>
       <c r="G79">
-        <v>-13.5053137435782</v>
+        <v>-17.38476825740929</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.34340389653731</v>
       </c>
       <c r="E80">
-        <v>-28.30923203267395</v>
+        <v>-29.73439035186489</v>
       </c>
       <c r="F80">
-        <v>-3.096196388302743</v>
+        <v>-3.412886892801339</v>
       </c>
       <c r="G80">
-        <v>-14.22773437006688</v>
+        <v>-16.57201111951775</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.17213258949491</v>
       </c>
       <c r="E81">
-        <v>-28.71654109881985</v>
+        <v>-34.30853628413961</v>
       </c>
       <c r="F81">
-        <v>-3.063633019122435</v>
+        <v>-4.065903479591105</v>
       </c>
       <c r="G81">
-        <v>-13.98658099080421</v>
+        <v>-16.36693772081483</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.99632146846907</v>
       </c>
       <c r="E82">
-        <v>-27.73529323694181</v>
+        <v>-37.16691134201815</v>
       </c>
       <c r="F82">
-        <v>-3.390103699501827</v>
+        <v>-4.91462731673426</v>
       </c>
       <c r="G82">
-        <v>-13.75881545770236</v>
+        <v>-14.71844163789813</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.82527117785516</v>
       </c>
       <c r="E83">
-        <v>-28.48710143474723</v>
+        <v>-33.04831857373004</v>
       </c>
       <c r="F83">
-        <v>-3.412132256932632</v>
+        <v>-4.470520544661941</v>
       </c>
       <c r="G83">
-        <v>-14.84462308112745</v>
+        <v>-15.78822953145868</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.65877765368577</v>
       </c>
       <c r="E84">
-        <v>-29.91449908433496</v>
+        <v>-34.80601632472624</v>
       </c>
       <c r="F84">
-        <v>-2.944427474867308</v>
+        <v>-5.083199349932507</v>
       </c>
       <c r="G84">
-        <v>-12.96880507821115</v>
+        <v>-16.61370744058488</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.49213903288018</v>
       </c>
       <c r="E85">
-        <v>-29.193067890173</v>
+        <v>-33.54313360736317</v>
       </c>
       <c r="F85">
-        <v>-3.304708692835416</v>
+        <v>-4.710444864174398</v>
       </c>
       <c r="G85">
-        <v>-14.61827777206194</v>
+        <v>-14.91704788589008</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.3266819949528</v>
       </c>
       <c r="E86">
-        <v>-30.23035561789596</v>
+        <v>-32.85922761306576</v>
       </c>
       <c r="F86">
-        <v>-3.499767415616431</v>
+        <v>-4.509912853749625</v>
       </c>
       <c r="G86">
-        <v>-13.86376637238833</v>
+        <v>-17.32639671846087</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.16786675890939</v>
       </c>
       <c r="E87">
-        <v>-32.40228873603279</v>
+        <v>-33.98317901211052</v>
       </c>
       <c r="F87">
-        <v>-3.281846314240132</v>
+        <v>-5.166923546858129</v>
       </c>
       <c r="G87">
-        <v>-12.91767701290264</v>
+        <v>-16.68711547737268</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.02142010835642</v>
       </c>
       <c r="E88">
-        <v>-32.46042981381728</v>
+        <v>-37.06190961520229</v>
       </c>
       <c r="F88">
-        <v>-3.38525835125354</v>
+        <v>-4.430200975760768</v>
       </c>
       <c r="G88">
-        <v>-13.10718257120714</v>
+        <v>-15.64292141137622</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.885372319137122</v>
       </c>
       <c r="E89">
-        <v>-33.09142738204606</v>
+        <v>-36.01095042445017</v>
       </c>
       <c r="F89">
-        <v>-3.3734581584776</v>
+        <v>-5.790731845449447</v>
       </c>
       <c r="G89">
-        <v>-12.95310647126392</v>
+        <v>-13.92700606855226</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.76031181908794</v>
       </c>
       <c r="E90">
-        <v>-33.10066999749572</v>
+        <v>-38.27357982001263</v>
       </c>
       <c r="F90">
-        <v>-3.146571697913999</v>
+        <v>-4.956557514551434</v>
       </c>
       <c r="G90">
-        <v>-14.3236011477931</v>
+        <v>-16.33051840933731</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.645877801538395</v>
       </c>
       <c r="E91">
-        <v>-35.50939249301963</v>
+        <v>-40.0838056052608</v>
       </c>
       <c r="F91">
-        <v>-3.313556065932019</v>
+        <v>-6.128896610308443</v>
       </c>
       <c r="G91">
-        <v>-13.29182162756891</v>
+        <v>-14.68487105085715</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.551620083059511</v>
       </c>
       <c r="E92">
-        <v>-38.62235383113538</v>
+        <v>-40.13266104709255</v>
       </c>
       <c r="F92">
-        <v>-3.194815339363073</v>
+        <v>-4.802407499272136</v>
       </c>
       <c r="G92">
-        <v>-13.08209856765608</v>
+        <v>-15.1299772091577</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.478796137112701</v>
       </c>
       <c r="E93">
-        <v>-37.48626159327606</v>
+        <v>-43.24313398874109</v>
       </c>
       <c r="F93">
-        <v>-3.877618267010425</v>
+        <v>-5.035361929050744</v>
       </c>
       <c r="G93">
-        <v>-13.82768473655582</v>
+        <v>-14.94481012078241</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.420716466471216</v>
       </c>
       <c r="E94">
-        <v>-39.88485615668181</v>
+        <v>-42.00579639325528</v>
       </c>
       <c r="F94">
-        <v>-3.497762443927485</v>
+        <v>-4.679348798524744</v>
       </c>
       <c r="G94">
-        <v>-13.18229222840213</v>
+        <v>-15.03807646498753</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.378539803789806</v>
       </c>
       <c r="E95">
-        <v>-40.80257179246925</v>
+        <v>-46.54553045154571</v>
       </c>
       <c r="F95">
-        <v>-3.450802396122874</v>
+        <v>-5.526204654540638</v>
       </c>
       <c r="G95">
-        <v>-13.50362205480764</v>
+        <v>-16.3969329186734</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.352351482929356</v>
       </c>
       <c r="E96">
-        <v>-43.94746113657608</v>
+        <v>-47.61336047221341</v>
       </c>
       <c r="F96">
-        <v>-2.847372433398474</v>
+        <v>-5.610905998016086</v>
       </c>
       <c r="G96">
-        <v>-13.29555261239167</v>
+        <v>-17.04555651927341</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.343312242738556</v>
       </c>
       <c r="E97">
-        <v>-43.93610825223885</v>
+        <v>-47.35338304367005</v>
       </c>
       <c r="F97">
-        <v>-3.905051220877667</v>
+        <v>-5.077589863580021</v>
       </c>
       <c r="G97">
-        <v>-13.37294654600876</v>
+        <v>-15.77433351655759</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.346215433600408</v>
       </c>
       <c r="E98">
-        <v>-46.64046538064251</v>
+        <v>-48.42768878216872</v>
       </c>
       <c r="F98">
-        <v>-3.297740386807483</v>
+        <v>-4.452995255001689</v>
       </c>
       <c r="G98">
-        <v>-14.82955016728715</v>
+        <v>-15.72773758809235</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.350472300738941</v>
       </c>
       <c r="E99">
-        <v>-47.30654730124572</v>
+        <v>-50.51409714019669</v>
       </c>
       <c r="F99">
-        <v>-3.771761779916537</v>
+        <v>-4.729266417126438</v>
       </c>
       <c r="G99">
-        <v>-13.65736710019693</v>
+        <v>-15.91570043217555</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.353897887494448</v>
       </c>
       <c r="E100">
-        <v>-51.86988603030113</v>
+        <v>-53.176334931855</v>
       </c>
       <c r="F100">
-        <v>-3.320238513042216</v>
+        <v>-4.412545822215449</v>
       </c>
       <c r="G100">
-        <v>-13.98372730054936</v>
+        <v>-16.22874561836903</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.350468567458666</v>
       </c>
       <c r="E101">
-        <v>-53.83128925970287</v>
+        <v>-54.24795415314862</v>
       </c>
       <c r="F101">
-        <v>-2.906161180685502</v>
+        <v>-4.568109295024278</v>
       </c>
       <c r="G101">
-        <v>-13.69274690037512</v>
+        <v>-16.68417736820657</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.346782973667615</v>
       </c>
       <c r="E102">
-        <v>-53.30038228822862</v>
+        <v>-55.40124213893357</v>
       </c>
       <c r="F102">
-        <v>-2.674961497061201</v>
+        <v>-4.289783274474245</v>
       </c>
       <c r="G102">
-        <v>-13.97569591707109</v>
+        <v>-17.21739038548928</v>
       </c>
     </row>
   </sheetData>
